--- a/research/traditional_assets/database/data/norway/norway_telecom_wireless.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_telecom_wireless.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.07049808429118773</v>
+        <v>-0.2058479532163743</v>
       </c>
       <c r="H2">
-        <v>-0.07049808429118773</v>
+        <v>-0.2058479532163743</v>
       </c>
       <c r="I2">
-        <v>-0.1310344827586207</v>
+        <v>-0.3035087719298246</v>
       </c>
       <c r="J2">
-        <v>-0.1310344827586207</v>
+        <v>-0.3035087719298246</v>
       </c>
       <c r="K2">
-        <v>-98.8</v>
+        <v>-4.17</v>
       </c>
       <c r="L2">
-        <v>-0.378544061302682</v>
+        <v>-0.243859649122807</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>52.2</v>
+        <v>1.48</v>
       </c>
       <c r="V2">
-        <v>0.446535500427716</v>
+        <v>0.03507109004739336</v>
       </c>
       <c r="W2">
-        <v>0.5581920903954802</v>
+        <v>-0.6214605067064083</v>
       </c>
       <c r="X2">
-        <v>0.2113495811342664</v>
+        <v>0.0773629867305619</v>
       </c>
       <c r="Y2">
-        <v>0.3468425092612138</v>
+        <v>-0.6988234934369701</v>
       </c>
       <c r="Z2">
-        <v>0.5642023346303502</v>
+        <v>4.329113924050633</v>
       </c>
       <c r="AA2">
-        <v>-0.07392996108949416</v>
+        <v>-1.313924050632912</v>
       </c>
       <c r="AB2">
-        <v>0.04417005200703837</v>
+        <v>0.07440720893342737</v>
       </c>
       <c r="AC2">
-        <v>-0.1181000130965325</v>
+        <v>-1.388331259566339</v>
       </c>
       <c r="AD2">
-        <v>874.1</v>
+        <v>4.37</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>874.1</v>
+        <v>4.37</v>
       </c>
       <c r="AG2">
-        <v>821.9</v>
+        <v>2.89</v>
       </c>
       <c r="AH2">
-        <v>0.8820383451059536</v>
+        <v>0.0938372342709899</v>
       </c>
       <c r="AI2">
-        <v>1.469816714309736</v>
+        <v>0.3490415335463259</v>
       </c>
       <c r="AJ2">
-        <v>0.8754793353216873</v>
+        <v>0.06409403415391439</v>
       </c>
       <c r="AK2">
-        <v>1.515023041474654</v>
+        <v>0.2617753623188406</v>
       </c>
       <c r="AL2">
-        <v>72.09999999999999</v>
+        <v>0.138</v>
       </c>
       <c r="AM2">
-        <v>71.985</v>
+        <v>0.111</v>
       </c>
       <c r="AN2">
-        <v>69.928</v>
+        <v>-2.312169312169313</v>
       </c>
       <c r="AO2">
-        <v>-0.4743411927877948</v>
+        <v>-37.60869565217391</v>
       </c>
       <c r="AP2">
-        <v>65.752</v>
+        <v>-1.529100529100529</v>
       </c>
       <c r="AQ2">
-        <v>-0.4750989789539488</v>
+        <v>-46.75675675675675</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ice Group ASA (OB:ICEGR)</t>
+          <t>Nortel AS (OB:NTEL)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.07049808429118773</v>
+        <v>-0.2058479532163743</v>
       </c>
       <c r="H3">
-        <v>-0.07049808429118773</v>
+        <v>-0.2058479532163743</v>
       </c>
       <c r="I3">
-        <v>-0.1310344827586207</v>
+        <v>-0.3035087719298246</v>
       </c>
       <c r="J3">
-        <v>-0.1310344827586207</v>
+        <v>-0.3035087719298246</v>
       </c>
       <c r="K3">
-        <v>-98.8</v>
+        <v>-4.17</v>
       </c>
       <c r="L3">
-        <v>-0.378544061302682</v>
+        <v>-0.243859649122807</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>52.2</v>
+        <v>1.48</v>
       </c>
       <c r="V3">
-        <v>0.446535500427716</v>
+        <v>0.03507109004739336</v>
       </c>
       <c r="W3">
-        <v>0.5581920903954802</v>
+        <v>-0.6214605067064083</v>
       </c>
       <c r="X3">
-        <v>0.2113495811342664</v>
+        <v>0.0773629867305619</v>
       </c>
       <c r="Y3">
-        <v>0.3468425092612138</v>
+        <v>-0.6988234934369701</v>
       </c>
       <c r="Z3">
-        <v>0.5642023346303502</v>
+        <v>4.329113924050633</v>
       </c>
       <c r="AA3">
-        <v>-0.07392996108949416</v>
+        <v>-1.313924050632912</v>
       </c>
       <c r="AB3">
-        <v>0.04417005200703837</v>
+        <v>0.07440720893342737</v>
       </c>
       <c r="AC3">
-        <v>-0.1181000130965325</v>
+        <v>-1.388331259566339</v>
       </c>
       <c r="AD3">
-        <v>874.1</v>
+        <v>4.37</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>874.1</v>
+        <v>4.37</v>
       </c>
       <c r="AG3">
-        <v>821.9</v>
+        <v>2.89</v>
       </c>
       <c r="AH3">
-        <v>0.8820383451059536</v>
+        <v>0.0938372342709899</v>
       </c>
       <c r="AI3">
-        <v>1.469816714309736</v>
+        <v>0.3490415335463259</v>
       </c>
       <c r="AJ3">
-        <v>0.8754793353216873</v>
+        <v>0.06409403415391439</v>
       </c>
       <c r="AK3">
-        <v>1.515023041474654</v>
+        <v>0.2617753623188406</v>
       </c>
       <c r="AL3">
-        <v>72.09999999999999</v>
+        <v>0.138</v>
       </c>
       <c r="AM3">
-        <v>71.985</v>
+        <v>0.111</v>
       </c>
       <c r="AN3">
-        <v>69.928</v>
+        <v>-2.312169312169313</v>
       </c>
       <c r="AO3">
-        <v>-0.4743411927877948</v>
+        <v>-37.60869565217391</v>
       </c>
       <c r="AP3">
-        <v>65.752</v>
+        <v>-1.529100529100529</v>
       </c>
       <c r="AQ3">
-        <v>-0.4750989789539488</v>
+        <v>-46.75675675675675</v>
       </c>
     </row>
   </sheetData>
